--- a/data/trans_orig/IP07A08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A08-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39884</t>
+          <t>39830</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34832</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49402</t>
+          <t>49640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66637</t>
+          <t>66634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85872</t>
+          <t>85558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37167</t>
+          <t>35846</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>26482</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40969</t>
+          <t>40475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52869</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72693</t>
+          <t>72794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50750</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66726</t>
+          <t>66542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>45640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61583</t>
+          <t>61777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100442</t>
+          <t>100066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123350</t>
+          <t>123597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,82%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>32776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48703</t>
+          <t>48386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33254</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>48767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70961</t>
+          <t>70372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93188</t>
+          <t>92047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>15355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>25451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38037</t>
+          <t>37833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41920</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58734</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75817</t>
+          <t>76407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30507</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>21045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>33685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61545</t>
+          <t>60665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,64%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>39159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55344</t>
+          <t>54706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>46143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62483</t>
+          <t>62972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90841</t>
+          <t>90229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112481</t>
+          <t>113603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31126</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47360</t>
+          <t>47545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>30757</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46905</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66640</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88804</t>
+          <t>88866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>156476</t>
+          <t>157380</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>186549</t>
+          <t>187675</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>173491</t>
+          <t>171764</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>203150</t>
+          <t>201130</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>338134</t>
+          <t>338003</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>380208</t>
+          <t>378401</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118213</t>
+          <t>117367</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>148109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>125080</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>154384</t>
+          <t>154784</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>252198</t>
+          <t>253439</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>293464</t>
+          <t>294176</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23945</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30241</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43377</t>
+          <t>42980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33502</t>
+          <t>33459</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48495</t>
+          <t>47767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67631</t>
+          <t>68080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86994</t>
+          <t>88199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>32279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>35891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44299</t>
+          <t>44823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63955</t>
+          <t>64473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57738</t>
+          <t>58291</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72497</t>
+          <t>72677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42795</t>
+          <t>43998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59006</t>
+          <t>59178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105828</t>
+          <t>106043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127837</t>
+          <t>127132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22825</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37141</t>
+          <t>37291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34955</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50783</t>
+          <t>50679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61829</t>
+          <t>62094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83004</t>
+          <t>83279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44840</t>
+          <t>44491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>38833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50794</t>
+          <t>50886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73964</t>
+          <t>74886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91156</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55747</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58097</t>
+          <t>57676</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59384</t>
+          <t>59558</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90130</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112503</t>
+          <t>113724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47317</t>
+          <t>47656</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>28026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43987</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62929</t>
+          <t>62273</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85734</t>
+          <t>85663</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>175415</t>
+          <t>176647</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>204360</t>
+          <t>205297</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>174190</t>
+          <t>173078</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>202715</t>
+          <t>202939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,47 +7152,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>61,03%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>378656</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>357244</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>399052</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>54,59%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>60,97%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>378656</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>358158</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>398169</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107566</t>
+          <t>106485</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>134727</t>
+          <t>135861</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>113575</t>
+          <t>112876</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142749</t>
+          <t>141458</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229339</t>
+          <t>228213</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267692</t>
+          <t>269308</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27865</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>29608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44378</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35010</t>
+          <t>35047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50638</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69871</t>
+          <t>69317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90561</t>
+          <t>89440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37972</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36438</t>
+          <t>36613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49291</t>
+          <t>49784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70339</t>
+          <t>69790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44249</t>
+          <t>44592</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61203</t>
+          <t>61808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47533</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64065</t>
+          <t>63545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97070</t>
+          <t>97882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120973</t>
+          <t>122002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34119</t>
+          <t>34406</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50676</t>
+          <t>50243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38601</t>
+          <t>39140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55251</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77234</t>
+          <t>77016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100762</t>
+          <t>99927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43722</t>
+          <t>43663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56070</t>
+          <t>56590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>41484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55933</t>
+          <t>55789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89015</t>
+          <t>88583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107636</t>
+          <t>107615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32670</t>
+          <t>31913</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34648</t>
+          <t>35095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53675</t>
+          <t>53734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58653</t>
+          <t>58627</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44482</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61490</t>
+          <t>61534</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90337</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114282</t>
+          <t>115476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63668</t>
+          <t>63627</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>38303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55437</t>
+          <t>55228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>90169</t>
+          <t>88482</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114220</t>
+          <t>113955</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>173857</t>
+          <t>173862</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>204970</t>
+          <t>207589</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>185330</t>
+          <t>185167</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>217812</t>
+          <t>216944</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>370818</t>
+          <t>368485</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>413054</t>
+          <t>416148</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>132538</t>
+          <t>129555</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>161904</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129991</t>
+          <t>131102</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>162502</t>
+          <t>162355</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>271021</t>
+          <t>270428</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>314186</t>
+          <t>315271</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
